--- a/src/时序数据预测-系列/单元时序预测-水质参数/TSM/result/样点8/样点8.xlsx
+++ b/src/时序数据预测-系列/单元时序预测-水质参数/TSM/result/样点8/样点8.xlsx
@@ -11,13 +11,15 @@
     <sheet name="holt_winters_lstm" sheetId="2" r:id="rId2"/>
     <sheet name="sarima" sheetId="3" r:id="rId3"/>
     <sheet name="sarima_lstm" sheetId="4" r:id="rId4"/>
+    <sheet name="sarima_lstm_v1" sheetId="5" r:id="rId5"/>
+    <sheet name="sarima_lstm_v2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="6">
   <si>
     <t>Train Score: %.2f RMSE</t>
   </si>
@@ -467,22 +469,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>18.37849549813734</v>
+        <v>18.3013763845993</v>
       </c>
       <c r="B2">
-        <v>26.31224924052002</v>
+        <v>26.11987362118934</v>
       </c>
       <c r="C2">
-        <v>13.97210080761208</v>
+        <v>13.92205012077439</v>
       </c>
       <c r="D2">
-        <v>20.95712012575565</v>
+        <v>20.37958647115315</v>
       </c>
       <c r="E2">
-        <v>0.2019195219623338</v>
+        <v>0.2135468041232188</v>
       </c>
       <c r="F2">
-        <v>1.321960524991001</v>
+        <v>1.239053133172589</v>
       </c>
     </row>
   </sheetData>
@@ -567,22 +569,122 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>26.59451947811962</v>
+        <v>27.03084472986018</v>
       </c>
       <c r="B2">
-        <v>27.5433668163556</v>
+        <v>27.56779793536786</v>
       </c>
       <c r="C2">
-        <v>19.5354504533913</v>
+        <v>19.92587748908453</v>
       </c>
       <c r="D2">
-        <v>18.13593304379457</v>
+        <v>19.1376600591068</v>
       </c>
       <c r="E2">
-        <v>0.1254899779344592</v>
+        <v>0.123937899416221</v>
       </c>
       <c r="F2">
-        <v>1.25074410120358</v>
+        <v>1.358367316069333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>30.41480423711757</v>
+      </c>
+      <c r="B2">
+        <v>23.91648243906211</v>
+      </c>
+      <c r="C2">
+        <v>22.00400549174737</v>
+      </c>
+      <c r="D2">
+        <v>16.54759939309256</v>
+      </c>
+      <c r="E2">
+        <v>0.3406358210650272</v>
+      </c>
+      <c r="F2">
+        <v>0.9759349512353478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>30.34704877009451</v>
+      </c>
+      <c r="B2">
+        <v>24.80988614610679</v>
+      </c>
+      <c r="C2">
+        <v>21.88432522357873</v>
+      </c>
+      <c r="D2">
+        <v>18.05396872840337</v>
+      </c>
+      <c r="E2">
+        <v>0.2904544485908378</v>
+      </c>
+      <c r="F2">
+        <v>1.048712521319972</v>
       </c>
     </row>
   </sheetData>
